--- a/cli/output/xlsxw/testdata/actor_0_rows.xlsx
+++ b/cli/output/xlsxw/testdata/actor_0_rows.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Go XLSX"/>
-  <workbookPr showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="204" windowHeight="8192" windowWidth="16384" xWindow="0" yWindow="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1" state="visible"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr iterateCount="100" refMode="A1" iterateDelta="0.001"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
@@ -33,14 +31,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,23 +64,37 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="0" numFmtId="0">
-      <alignment horizontal="general" indent="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="0" numFmtId="0">
-      <alignment horizontal="general" indent="0" shrinkToFit="0" textRotation="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
+      <alignment/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -83,44 +104,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -150,12 +171,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -194,233 +215,163 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="12.85"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="true" max="3" min="2" width="32"/>
+    <col customWidth="true" max="4" min="4" width="20"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>